--- a/backend/DATA_EVALUATION.xlsx
+++ b/backend/DATA_EVALUATION.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\vonje\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Randel\Downloads\Von Files\Von_Thesis\Von_Thesis\backend\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5965B41E-175D-4327-840C-CCB4E95F7EA1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{809DD107-3D17-4F41-956B-F0CB428EF400}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3348" yWindow="3348" windowWidth="17280" windowHeight="8880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="DATA_EVALUATION" sheetId="5" r:id="rId1"/>
@@ -3074,6 +3074,30 @@
       </fill>
     </dxf>
     <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF5B3F86"/>
+          <bgColor rgb="FF5B3F86"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
       <border>
         <left style="thin">
           <color rgb="FF5B3F86"/>
@@ -3108,1736 +3132,1736 @@
     <dxf>
       <fill>
         <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
           <fgColor rgb="FF5B3F86"/>
           <bgColor rgb="FF5B3F86"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
         </patternFill>
       </fill>
     </dxf>
@@ -4876,728 +4900,728 @@
     <dxf>
       <fill>
         <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
           <fgColor rgb="FF5B3F86"/>
           <bgColor rgb="FF5B3F86"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
         </patternFill>
       </fill>
     </dxf>
@@ -5636,200 +5660,200 @@
     <dxf>
       <fill>
         <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
           <fgColor rgb="FF5B3F86"/>
           <bgColor rgb="FF5B3F86"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
         </patternFill>
       </fill>
     </dxf>
@@ -5868,744 +5892,744 @@
     <dxf>
       <fill>
         <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
           <fgColor rgb="FF5B3F86"/>
           <bgColor rgb="FF5B3F86"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
         </patternFill>
       </fill>
     </dxf>
@@ -6644,408 +6668,408 @@
     <dxf>
       <fill>
         <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
           <fgColor rgb="FF5B3F86"/>
           <bgColor rgb="FF5B3F86"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
         </patternFill>
       </fill>
     </dxf>
@@ -7065,37 +7089,13 @@
         </bottom>
       </border>
     </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF5B3F86"/>
-          <bgColor rgb="FF5B3F86"/>
-        </patternFill>
-      </fill>
-    </dxf>
   </dxfs>
   <tableStyles count="388">
     <tableStyle name="SURVEY RESULTS-style" pivot="0" count="4" xr9:uid="{00000000-0011-0000-FFFF-FFFF00000000}">
-      <tableStyleElement type="wholeTable" size="0" dxfId="784"/>
-      <tableStyleElement type="headerRow" dxfId="787"/>
-      <tableStyleElement type="firstRowStripe" dxfId="786"/>
-      <tableStyleElement type="secondRowStripe" dxfId="785"/>
+      <tableStyleElement type="wholeTable" size="0" dxfId="787"/>
+      <tableStyleElement type="headerRow" dxfId="786"/>
+      <tableStyleElement type="firstRowStripe" dxfId="785"/>
+      <tableStyleElement type="secondRowStripe" dxfId="784"/>
     </tableStyle>
     <tableStyle name="2022 -2025 PRC DATA RECORD-style" pivot="0" count="2" xr9:uid="{00000000-0011-0000-FFFF-FFFF01000000}">
       <tableStyleElement type="firstRowStripe" dxfId="783"/>
@@ -7198,10 +7198,10 @@
       <tableStyleElement type="secondRowStripe" dxfId="734"/>
     </tableStyle>
     <tableStyle name="DATA_MODEL-style" pivot="0" count="4" xr9:uid="{00000000-0011-0000-FFFF-FFFF1A000000}">
-      <tableStyleElement type="wholeTable" size="0" dxfId="730"/>
-      <tableStyleElement type="headerRow" dxfId="733"/>
-      <tableStyleElement type="firstRowStripe" dxfId="732"/>
-      <tableStyleElement type="secondRowStripe" dxfId="731"/>
+      <tableStyleElement type="wholeTable" size="0" dxfId="733"/>
+      <tableStyleElement type="headerRow" dxfId="732"/>
+      <tableStyleElement type="firstRowStripe" dxfId="731"/>
+      <tableStyleElement type="secondRowStripe" dxfId="730"/>
     </tableStyle>
     <tableStyle name="DATA_MODEL-style 2" pivot="0" count="2" xr9:uid="{00000000-0011-0000-FFFF-FFFF1B000000}">
       <tableStyleElement type="firstRowStripe" dxfId="729"/>
@@ -7388,10 +7388,10 @@
       <tableStyleElement type="secondRowStripe" dxfId="638"/>
     </tableStyle>
     <tableStyle name="DATA_EVALUATION-style" pivot="0" count="4" xr9:uid="{00000000-0011-0000-FFFF-FFFF49000000}">
-      <tableStyleElement type="wholeTable" size="0" dxfId="634"/>
-      <tableStyleElement type="headerRow" dxfId="637"/>
-      <tableStyleElement type="firstRowStripe" dxfId="636"/>
-      <tableStyleElement type="secondRowStripe" dxfId="635"/>
+      <tableStyleElement type="wholeTable" size="0" dxfId="637"/>
+      <tableStyleElement type="headerRow" dxfId="636"/>
+      <tableStyleElement type="firstRowStripe" dxfId="635"/>
+      <tableStyleElement type="secondRowStripe" dxfId="634"/>
     </tableStyle>
     <tableStyle name="DATA_EVALUATION-style 2" pivot="0" count="2" xr9:uid="{00000000-0011-0000-FFFF-FFFF4A000000}">
       <tableStyleElement type="firstRowStripe" dxfId="633"/>
@@ -7442,10 +7442,10 @@
       <tableStyleElement type="secondRowStripe" dxfId="610"/>
     </tableStyle>
     <tableStyle name="DATA_ALL1-style" pivot="0" count="4" xr9:uid="{00000000-0011-0000-FFFF-FFFF56000000}">
-      <tableStyleElement type="wholeTable" size="0" dxfId="606"/>
-      <tableStyleElement type="headerRow" dxfId="609"/>
-      <tableStyleElement type="firstRowStripe" dxfId="608"/>
-      <tableStyleElement type="secondRowStripe" dxfId="607"/>
+      <tableStyleElement type="wholeTable" size="0" dxfId="609"/>
+      <tableStyleElement type="headerRow" dxfId="608"/>
+      <tableStyleElement type="firstRowStripe" dxfId="607"/>
+      <tableStyleElement type="secondRowStripe" dxfId="606"/>
     </tableStyle>
     <tableStyle name="DATA_ALL1-style 2" pivot="0" count="2" xr9:uid="{00000000-0011-0000-FFFF-FFFF57000000}">
       <tableStyleElement type="firstRowStripe" dxfId="605"/>
@@ -7628,10 +7628,10 @@
       <tableStyleElement type="secondRowStripe" dxfId="516"/>
     </tableStyle>
     <tableStyle name="DATA_DRAFT (EVALUATION)-style" pivot="0" count="4" xr9:uid="{00000000-0011-0000-FFFF-FFFF84000000}">
-      <tableStyleElement type="wholeTable" size="0" dxfId="512"/>
-      <tableStyleElement type="headerRow" dxfId="515"/>
-      <tableStyleElement type="firstRowStripe" dxfId="514"/>
-      <tableStyleElement type="secondRowStripe" dxfId="513"/>
+      <tableStyleElement type="wholeTable" size="0" dxfId="515"/>
+      <tableStyleElement type="headerRow" dxfId="514"/>
+      <tableStyleElement type="firstRowStripe" dxfId="513"/>
+      <tableStyleElement type="secondRowStripe" dxfId="512"/>
     </tableStyle>
     <tableStyle name="DATA_DRAFT (EVALUATION)-style 2" pivot="0" count="2" xr9:uid="{00000000-0011-0000-FFFF-FFFF85000000}">
       <tableStyleElement type="firstRowStripe" dxfId="511"/>
@@ -8066,10 +8066,10 @@
       <tableStyleElement type="secondRowStripe" dxfId="296"/>
     </tableStyle>
     <tableStyle name="DATA_DRAFT (MODEL)-style" pivot="0" count="4" xr9:uid="{00000000-0011-0000-FFFF-FFFFF1000000}">
-      <tableStyleElement type="wholeTable" size="0" dxfId="292"/>
-      <tableStyleElement type="headerRow" dxfId="295"/>
-      <tableStyleElement type="firstRowStripe" dxfId="294"/>
-      <tableStyleElement type="secondRowStripe" dxfId="293"/>
+      <tableStyleElement type="wholeTable" size="0" dxfId="295"/>
+      <tableStyleElement type="headerRow" dxfId="294"/>
+      <tableStyleElement type="firstRowStripe" dxfId="293"/>
+      <tableStyleElement type="secondRowStripe" dxfId="292"/>
     </tableStyle>
     <tableStyle name="DATA_DRAFT (MODEL)-style 2" pivot="0" count="2" xr9:uid="{00000000-0011-0000-FFFF-FFFFF2000000}">
       <tableStyleElement type="firstRowStripe" dxfId="291"/>
@@ -9092,20 +9092,20 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
   <dimension ref="A1:CT37"/>
-  <sheetFormatPr defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="12.7109375" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="1:98" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:98" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="11" t="s">
         <v>120</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="D1" s="1" t="s">
         <v>121</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>122</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>123</v>
       </c>
       <c r="E1" s="2" t="s">
         <v>117</v>
@@ -9390,7 +9390,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="2" spans="1:98" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:98" ht="15" x14ac:dyDescent="0.25">
       <c r="A2" s="12" t="s">
         <v>129</v>
       </c>
@@ -9676,7 +9676,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:98" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:98" ht="15" x14ac:dyDescent="0.25">
       <c r="A3" s="12" t="s">
         <v>130</v>
       </c>
@@ -9958,7 +9958,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:98" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:98" ht="15" x14ac:dyDescent="0.25">
       <c r="A4" s="12" t="s">
         <v>131</v>
       </c>
@@ -10244,7 +10244,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:98" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:98" ht="15" x14ac:dyDescent="0.25">
       <c r="A5" s="12" t="s">
         <v>132</v>
       </c>
@@ -10534,7 +10534,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="6" spans="1:98" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:98" ht="15" x14ac:dyDescent="0.25">
       <c r="A6" s="12" t="s">
         <v>133</v>
       </c>
@@ -10820,7 +10820,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="7" spans="1:98" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:98" ht="15" x14ac:dyDescent="0.25">
       <c r="A7" s="12" t="s">
         <v>134</v>
       </c>
@@ -11102,7 +11102,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="8" spans="1:98" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:98" ht="15" x14ac:dyDescent="0.25">
       <c r="A8" s="12" t="s">
         <v>135</v>
       </c>
@@ -11384,7 +11384,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="9" spans="1:98" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:98" ht="15" x14ac:dyDescent="0.25">
       <c r="A9" s="12" t="s">
         <v>136</v>
       </c>
@@ -11666,7 +11666,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="10" spans="1:98" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:98" ht="15" x14ac:dyDescent="0.25">
       <c r="A10" s="12" t="s">
         <v>137</v>
       </c>
@@ -11948,7 +11948,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="11" spans="1:98" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:98" ht="15" x14ac:dyDescent="0.25">
       <c r="A11" s="12" t="s">
         <v>138</v>
       </c>
@@ -12236,7 +12236,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="1:98" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:98" ht="15" x14ac:dyDescent="0.25">
       <c r="A12" s="12" t="s">
         <v>139</v>
       </c>
@@ -12518,7 +12518,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="13" spans="1:98" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:98" ht="15" x14ac:dyDescent="0.25">
       <c r="A13" s="12" t="s">
         <v>140</v>
       </c>
@@ -12800,7 +12800,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="14" spans="1:98" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:98" ht="15" x14ac:dyDescent="0.25">
       <c r="A14" s="12" t="s">
         <v>141</v>
       </c>
@@ -13082,7 +13082,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="15" spans="1:98" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:98" ht="15" x14ac:dyDescent="0.25">
       <c r="A15" s="12" t="s">
         <v>142</v>
       </c>
@@ -13364,7 +13364,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="16" spans="1:98" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:98" ht="15" x14ac:dyDescent="0.25">
       <c r="A16" s="12" t="s">
         <v>143</v>
       </c>
@@ -13646,7 +13646,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="17" spans="1:98" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:98" ht="15" x14ac:dyDescent="0.25">
       <c r="A17" s="12" t="s">
         <v>144</v>
       </c>
@@ -13932,7 +13932,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="18" spans="1:98" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:98" ht="15" x14ac:dyDescent="0.25">
       <c r="A18" s="12" t="s">
         <v>149</v>
       </c>
@@ -14220,7 +14220,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="19" spans="1:98" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:98" ht="15" x14ac:dyDescent="0.25">
       <c r="A19" s="12" t="s">
         <v>127</v>
       </c>
@@ -14508,7 +14508,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="20" spans="1:98" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:98" ht="15" x14ac:dyDescent="0.25">
       <c r="A20" s="12" t="s">
         <v>147</v>
       </c>
@@ -14796,7 +14796,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="21" spans="1:98" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:98" ht="15" x14ac:dyDescent="0.25">
       <c r="A21" s="12" t="s">
         <v>145</v>
       </c>
@@ -15082,7 +15082,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="22" spans="1:98" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:98" ht="15" x14ac:dyDescent="0.25">
       <c r="A22" s="12" t="s">
         <v>148</v>
       </c>
@@ -15366,7 +15366,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="23" spans="1:98" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:98" ht="15" x14ac:dyDescent="0.25">
       <c r="A23" s="12" t="s">
         <v>151</v>
       </c>
@@ -15650,7 +15650,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="24" spans="1:98" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:98" ht="15" x14ac:dyDescent="0.25">
       <c r="A24" s="12" t="s">
         <v>157</v>
       </c>
@@ -15934,7 +15934,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="25" spans="1:98" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:98" ht="15" x14ac:dyDescent="0.25">
       <c r="A25" s="12" t="s">
         <v>116</v>
       </c>
@@ -16216,7 +16216,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="26" spans="1:98" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:98" ht="15" x14ac:dyDescent="0.25">
       <c r="A26" s="12" t="s">
         <v>128</v>
       </c>
@@ -16510,7 +16510,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="27" spans="1:98" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:98" ht="15" x14ac:dyDescent="0.25">
       <c r="A27" s="12" t="s">
         <v>155</v>
       </c>
@@ -16802,7 +16802,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="28" spans="1:98" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:98" ht="15" x14ac:dyDescent="0.25">
       <c r="A28" s="12" t="s">
         <v>159</v>
       </c>
@@ -17086,7 +17086,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="29" spans="1:98" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:98" ht="15" x14ac:dyDescent="0.25">
       <c r="A29" s="12" t="s">
         <v>156</v>
       </c>
@@ -17372,7 +17372,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="30" spans="1:98" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:98" ht="15" x14ac:dyDescent="0.25">
       <c r="A30" s="12" t="s">
         <v>172</v>
       </c>
@@ -17654,7 +17654,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="31" spans="1:98" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:98" ht="15" x14ac:dyDescent="0.25">
       <c r="A31" s="12" t="s">
         <v>152</v>
       </c>
@@ -17940,7 +17940,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="32" spans="1:98" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:98" ht="15" x14ac:dyDescent="0.25">
       <c r="A32" s="12" t="s">
         <v>150</v>
       </c>
@@ -18232,7 +18232,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="33" spans="1:98" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:98" ht="15" x14ac:dyDescent="0.25">
       <c r="A33" s="12" t="s">
         <v>146</v>
       </c>
@@ -18514,7 +18514,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="34" spans="1:98" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:98" ht="15" x14ac:dyDescent="0.25">
       <c r="A34" s="12" t="s">
         <v>153</v>
       </c>
@@ -18798,7 +18798,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="35" spans="1:98" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:98" ht="15" x14ac:dyDescent="0.25">
       <c r="A35" s="12" t="s">
         <v>154</v>
       </c>
@@ -19082,7 +19082,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="36" spans="1:98" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:98" ht="15" x14ac:dyDescent="0.25">
       <c r="A36" s="12" t="s">
         <v>158</v>
       </c>
@@ -19376,7 +19376,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="37" spans="1:98" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:98" ht="15" x14ac:dyDescent="0.25">
       <c r="A37" s="12" t="s">
         <v>128</v>
       </c>

--- a/backend/DATA_EVALUATION.xlsx
+++ b/backend/DATA_EVALUATION.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Randel\Downloads\Von Files\Von_Thesis\Von_Thesis\backend\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{809DD107-3D17-4F41-956B-F0CB428EF400}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{287BD50D-AC2C-4049-975F-261A2B4F8731}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -9093,19 +9093,22 @@
   </sheetPr>
   <dimension ref="A1:CT37"/>
   <sheetFormatPr defaultColWidth="12.7109375" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="15" max="15" width="32.140625" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:98" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="11" t="s">
         <v>120</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="D1" s="1" t="s">
         <v>122</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>123</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>121</v>
       </c>
       <c r="E1" s="2" t="s">
         <v>117</v>
@@ -19670,11 +19673,12 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
   <tableParts count="4">
-    <tablePart r:id="rId1"/>
     <tablePart r:id="rId2"/>
     <tablePart r:id="rId3"/>
     <tablePart r:id="rId4"/>
+    <tablePart r:id="rId5"/>
   </tableParts>
 </worksheet>
 </file>
--- a/backend/DATA_EVALUATION.xlsx
+++ b/backend/DATA_EVALUATION.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Randel\Downloads\Von Files\Von_Thesis\Von_Thesis\backend\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{287BD50D-AC2C-4049-975F-261A2B4F8731}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{830A2E7A-5E03-444B-A43D-FB006D9063C3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -9102,13 +9102,13 @@
         <v>120</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="D1" s="1" t="s">
         <v>123</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>121</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>122</v>
       </c>
       <c r="E1" s="2" t="s">
         <v>117</v>

--- a/backend/DATA_EVALUATION.xlsx
+++ b/backend/DATA_EVALUATION.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Randel\Downloads\Von Files\Von_Thesis\Von_Thesis\backend\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{830A2E7A-5E03-444B-A43D-FB006D9063C3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EC3D9758-29B1-4342-8514-CA5A66832A0C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3510" yWindow="3510" windowWidth="22845" windowHeight="12285" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="DATA_EVALUATION" sheetId="5" r:id="rId1"/>
@@ -9102,13 +9102,13 @@
         <v>120</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="D1" s="1" t="s">
         <v>121</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>122</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>123</v>
       </c>
       <c r="E1" s="2" t="s">
         <v>117</v>
